--- a/251209_Plasma_impedance_calculator_single frequency_900W_8Torr.xlsx
+++ b/251209_Plasma_impedance_calculator_single frequency_900W_8Torr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASMK\Desktop\Calculator\250801\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pnd\Coding\260309_plasma_calculator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EBD1E1F-FECC-4FA5-85D1-F000433CCBB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EDD4010-8127-4540-9E7A-20218B38D910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{A0C19483-6F59-4CB5-A669-8AEDA5BC838C}"/>
+    <workbookView xWindow="-16320" yWindow="-4005" windowWidth="16440" windowHeight="28440" xr2:uid="{A0C19483-6F59-4CB5-A669-8AEDA5BC838C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -599,14 +599,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Aptos Narrow"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -673,7 +673,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -15979,7 +15979,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -16296,28 +16296,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75B303DF-8F76-4877-ABFD-D4B01B341FED}">
   <dimension ref="A1:Q117"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E1" s="2"/>
       <c r="F1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E2" s="1"/>
       <c r="F2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>2</v>
       </c>
@@ -16331,7 +16331,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>0</v>
       </c>
@@ -16347,7 +16347,7 @@
       </c>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" t="s">
         <v>5</v>
@@ -16361,7 +16361,7 @@
       </c>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" t="s">
         <v>6</v>
@@ -16375,7 +16375,7 @@
       </c>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" t="s">
         <v>7</v>
@@ -16389,7 +16389,7 @@
       </c>
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
       <c r="B8" t="s">
         <v>8</v>
@@ -16403,7 +16403,7 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
       <c r="B9" t="s">
         <v>9</v>
@@ -16416,7 +16416,7 @@
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
       <c r="B10" t="s">
         <v>10</v>
@@ -16429,10 +16429,10 @@
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
@@ -16447,7 +16447,7 @@
       </c>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
       <c r="B13" t="s">
         <v>16</v>
@@ -16461,7 +16461,7 @@
       </c>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="B14" t="s">
         <v>17</v>
@@ -16474,7 +16474,7 @@
       </c>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
       <c r="B15" t="s">
         <v>17</v>
@@ -16492,7 +16492,7 @@
         <v>27539.704153500003</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
       <c r="B16" t="s">
         <v>18</v>
@@ -16514,7 +16514,7 @@
         <v>226.88866418823523</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" t="s">
         <v>19</v>
@@ -16531,7 +16531,7 @@
         <v>2.8996363972734967E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" t="s">
         <v>19</v>
@@ -16545,7 +16545,7 @@
       </c>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
       <c r="B19" t="s">
         <v>20</v>
@@ -16558,10 +16558,10 @@
       </c>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>27</v>
       </c>
@@ -16577,7 +16577,7 @@
       </c>
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
       <c r="B22" t="s">
         <v>71</v>
@@ -16595,10 +16595,10 @@
         <v>2.503134705878571E-5</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>30</v>
       </c>
@@ -16614,7 +16614,7 @@
         <v>8.1950628627785859E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" t="s">
         <v>29</v>
@@ -16628,7 +16628,7 @@
         <v>7.9696504601983451E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" t="s">
         <v>31</v>
@@ -16639,7 +16639,7 @@
       </c>
       <c r="E26" s="1"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" t="s">
         <v>32</v>
@@ -16650,10 +16650,10 @@
       </c>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>33</v>
       </c>
@@ -16669,14 +16669,14 @@
       </c>
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
       <c r="K30">
         <f>SQRT(C31)</f>
         <v>1.4184498581197715</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>35</v>
       </c>
@@ -16691,7 +16691,7 @@
       </c>
       <c r="E31" s="2"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
       <c r="B32" t="s">
         <v>37</v>
@@ -16705,7 +16705,7 @@
       </c>
       <c r="E32" s="1"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="5"/>
       <c r="B33" t="s">
         <v>38</v>
@@ -16716,10 +16716,10 @@
       </c>
       <c r="E33" s="1"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>39</v>
       </c>
@@ -16732,7 +16732,7 @@
       </c>
       <c r="E35" s="1"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
       <c r="B36" t="s">
         <v>41</v>
@@ -16743,7 +16743,7 @@
       </c>
       <c r="E36" s="1"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="5"/>
       <c r="B37" t="s">
         <v>42</v>
@@ -16754,10 +16754,10 @@
       </c>
       <c r="E37" s="1"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="3"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>43</v>
       </c>
@@ -16773,7 +16773,7 @@
       </c>
       <c r="E39" s="1"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="5"/>
       <c r="B40" t="s">
         <v>76</v>
@@ -16787,7 +16787,7 @@
       </c>
       <c r="E40" s="1"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="5"/>
       <c r="B41" s="4" t="s">
         <v>44</v>
@@ -16800,7 +16800,7 @@
       </c>
       <c r="E41" s="2"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="5"/>
       <c r="B42" t="s">
         <v>77</v>
@@ -16814,10 +16814,10 @@
       </c>
       <c r="E42" s="1"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>45</v>
       </c>
@@ -16832,10 +16832,10 @@
       </c>
       <c r="E44" s="2"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="3"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>47</v>
       </c>
@@ -16851,7 +16851,7 @@
       </c>
       <c r="E46" s="1"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="5"/>
       <c r="B47" t="s">
         <v>80</v>
@@ -16865,10 +16865,10 @@
       </c>
       <c r="E47" s="1"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>48</v>
       </c>
@@ -16884,13 +16884,13 @@
       </c>
       <c r="E49" s="1"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="3"/>
       <c r="K50">
         <v>8.2452397714329748E-5</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>50</v>
       </c>
@@ -16906,10 +16906,10 @@
       </c>
       <c r="E51" s="1"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="3"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>53</v>
       </c>
@@ -16921,7 +16921,7 @@
       </c>
       <c r="E53" s="2"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>54</v>
       </c>
@@ -16934,10 +16934,10 @@
       </c>
       <c r="E54" s="1"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="3"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>55</v>
       </c>
@@ -16947,7 +16947,7 @@
       </c>
       <c r="E56" s="1"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>56</v>
       </c>
@@ -16957,10 +16957,10 @@
       </c>
       <c r="E57" s="1"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="3"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>57</v>
       </c>
@@ -16980,7 +16980,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="3"/>
       <c r="C60">
         <f>C59*1000000</f>
@@ -16991,10 +16991,10 @@
       </c>
       <c r="E60" s="1"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="3"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>59</v>
       </c>
@@ -17010,7 +17010,7 @@
       </c>
       <c r="E62" s="1"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>60</v>
       </c>
@@ -17026,7 +17026,7 @@
       </c>
       <c r="E63" s="1"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>61</v>
       </c>
@@ -17042,7 +17042,7 @@
       </c>
       <c r="E64" s="1"/>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="3"/>
       <c r="F65" t="s">
         <v>137</v>
@@ -17054,7 +17054,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
         <v>62</v>
       </c>
@@ -17085,7 +17085,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="5"/>
       <c r="B67" t="s">
         <v>84</v>
@@ -17111,7 +17111,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="5"/>
       <c r="B68" t="s">
         <v>83</v>
@@ -17146,7 +17146,7 @@
         <v>0.50967234442142495</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>13</v>
       </c>
@@ -17187,7 +17187,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="5"/>
       <c r="B70" t="s">
         <v>87</v>
@@ -17208,7 +17208,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="5"/>
       <c r="B71" t="s">
         <v>88</v>
@@ -17222,7 +17222,7 @@
       </c>
       <c r="E71" s="1"/>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
         <v>106</v>
       </c>
@@ -17233,7 +17233,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B74" t="s">
         <v>107</v>
       </c>
@@ -17244,7 +17244,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
         <v>96</v>
       </c>
@@ -17256,7 +17256,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="5"/>
       <c r="C77">
         <f>C76*1000000</f>
@@ -17266,7 +17266,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>97</v>
       </c>
@@ -17278,7 +17278,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>98</v>
       </c>
@@ -17290,7 +17290,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>99</v>
       </c>
@@ -17302,7 +17302,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>113</v>
       </c>
@@ -17314,7 +17314,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>100</v>
       </c>
@@ -17326,7 +17326,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>114</v>
       </c>
@@ -17338,7 +17338,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>118</v>
       </c>
@@ -17354,7 +17354,7 @@
         <v>0.73028558094956142</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>123</v>
       </c>
@@ -17369,7 +17369,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="E88" t="s">
         <v>137</v>
       </c>
@@ -17392,7 +17392,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>124</v>
       </c>
@@ -17445,7 +17445,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>125</v>
       </c>
@@ -17498,7 +17498,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>144</v>
       </c>
@@ -17521,7 +17521,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>126</v>
       </c>
@@ -17533,7 +17533,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>128</v>
       </c>
@@ -17542,7 +17542,7 @@
         <v>948629.80707743682</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>129</v>
       </c>
@@ -17554,7 +17554,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>130</v>
       </c>
@@ -17566,7 +17566,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>133</v>
       </c>
@@ -17578,7 +17578,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>134</v>
       </c>
@@ -17590,7 +17590,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>101</v>
       </c>
@@ -17604,7 +17604,7 @@
         <v>101.55115701055705</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>117</v>
       </c>
@@ -17615,7 +17615,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>119</v>
       </c>
@@ -17627,7 +17627,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>102</v>
       </c>
@@ -17636,7 +17636,7 @@
         <v>729.8557976234946</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>108</v>
       </c>
@@ -17645,7 +17645,7 @@
         <v>1.5989242614132864</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>109</v>
       </c>
@@ -17654,7 +17654,7 @@
         <v>91.611611940053663</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>110</v>
       </c>
@@ -17663,7 +17663,7 @@
         <v>675.12325474042757</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>111</v>
       </c>
@@ -17672,19 +17672,19 @@
         <v>361.26113315639435</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C112">
         <f>C109*(C78/(C78+C79))</f>
         <v>171.80313784718339</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C113">
         <f>C110*(C79/(C78+C79))</f>
         <v>269.32859221265085</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>103</v>
       </c>
@@ -17693,7 +17693,7 @@
         <v>441.13173005983424</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>112</v>
       </c>
@@ -17702,24 +17702,24 @@
         <v>-9.4140103207635875</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>116</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A66:A68"/>
+    <mergeCell ref="A69:A71"/>
+    <mergeCell ref="A76:A77"/>
     <mergeCell ref="A35:A37"/>
     <mergeCell ref="A4:A10"/>
     <mergeCell ref="A12:A19"/>
     <mergeCell ref="A21:A22"/>
     <mergeCell ref="A24:A27"/>
     <mergeCell ref="A31:A33"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A66:A68"/>
-    <mergeCell ref="A69:A71"/>
-    <mergeCell ref="A76:A77"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17730,8 +17730,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D2E7687-BDAA-4F33-9641-B209E360CDA7}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/251209_Plasma_impedance_calculator_single frequency_900W_8Torr.xlsx
+++ b/251209_Plasma_impedance_calculator_single frequency_900W_8Torr.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pnd\Coding\260309_plasma_calculator\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASMK\Coding\260309_Plasma_Calculator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EDD4010-8127-4540-9E7A-20218B38D910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CED83B57-2AC3-4573-BA9F-83E15E2CD9A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-4005" windowWidth="16440" windowHeight="28440" xr2:uid="{A0C19483-6F59-4CB5-A669-8AEDA5BC838C}"/>
+    <workbookView xWindow="-19200" yWindow="-4155" windowWidth="18600" windowHeight="21705" xr2:uid="{A0C19483-6F59-4CB5-A669-8AEDA5BC838C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -599,14 +599,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -673,7 +673,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -15975,11 +15975,657 @@
     </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>446210</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>16852</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2126351" cy="253980"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="28" name="TextBox 27">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C18A4D5-DDC3-4B0F-81E1-D63004B29464}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="13276385" y="3617302"/>
+              <a:ext cx="2126351" cy="253980"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1500" i="1" kern="1200">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐴</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑒𝑓𝑓</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=2</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝜋</m:t>
+                    </m:r>
+                    <m:sSup>
+                      <m:sSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSupPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑅</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSup>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>h</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑙</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>+2</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="ko-KR" altLang="en-US" sz="1500" b="0" i="1" kern="1200">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝜋</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑅𝑙</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>h</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑅</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1500" kern="1200"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="28" name="TextBox 27">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C18A4D5-DDC3-4B0F-81E1-D63004B29464}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="13276385" y="3617302"/>
+              <a:ext cx="2126351" cy="253980"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="0" kern="1200">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐴_𝑒𝑓𝑓=2</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="0" kern="1200">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝜋𝑅^2 ℎ_𝑙+2</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="ko-KR" altLang="en-US" sz="1500" b="0" i="0" kern="1200">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝜋</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="0" kern="1200">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑅𝑙ℎ_𝑅</a:t>
+              </a:r>
+              <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1500" kern="1200"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>436685</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>159727</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2250616" cy="528286"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="34" name="TextBox 33">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62FCBDF1-8FDC-49A5-B8D4-5105C5DF44AE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="13266860" y="4103077"/>
+              <a:ext cx="2250616" cy="528286"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1500" i="1" kern="1200">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑑</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑒𝑓𝑓</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:f>
+                      <m:fPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:fPr>
+                      <m:num>
+                        <m:r>
+                          <a:rPr lang="ko-KR" altLang="en-US" sz="1500" b="0" i="1" kern="1200">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝜋</m:t>
+                        </m:r>
+                        <m:sSup>
+                          <m:sSupPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSupPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑅</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sup>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>2</m:t>
+                            </m:r>
+                          </m:sup>
+                        </m:sSup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑙</m:t>
+                        </m:r>
+                      </m:num>
+                      <m:den>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝐴</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑒𝑓𝑓</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:den>
+                    </m:f>
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:f>
+                      <m:fPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:fPr>
+                      <m:num>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>1</m:t>
+                        </m:r>
+                      </m:num>
+                      <m:den>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:den>
+                    </m:f>
+                    <m:f>
+                      <m:fPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:fPr>
+                      <m:num>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑅𝑙</m:t>
+                        </m:r>
+                      </m:num>
+                      <m:den>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑅</m:t>
+                        </m:r>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>h</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑙</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>+</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑙</m:t>
+                        </m:r>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>h</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="1" kern="1200">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑅</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:den>
+                    </m:f>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1500" kern="1200"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="34" name="TextBox 33">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62FCBDF1-8FDC-49A5-B8D4-5105C5DF44AE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="13266860" y="4103077"/>
+              <a:ext cx="2250616" cy="528286"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="0" kern="1200">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑑_𝑒𝑓𝑓=(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="ko-KR" altLang="en-US" sz="1500" b="0" i="0" kern="1200">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝜋</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1500" b="0" i="0" kern="1200">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑅^2 𝑙)/𝐴_𝑒𝑓𝑓 =1/2  𝑅𝑙/(𝑅ℎ_𝑙+𝑙ℎ_𝑅 )</a:t>
+              </a:r>
+              <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1500" kern="1200"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -16296,28 +16942,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75B303DF-8F76-4877-ABFD-D4B01B341FED}">
   <dimension ref="A1:Q117"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.09765625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E1" s="2"/>
       <c r="F1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E2" s="1"/>
       <c r="F2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>2</v>
       </c>
@@ -16331,7 +16977,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>0</v>
       </c>
@@ -16347,7 +16993,7 @@
       </c>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" t="s">
         <v>5</v>
@@ -16361,7 +17007,7 @@
       </c>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" t="s">
         <v>6</v>
@@ -16375,7 +17021,7 @@
       </c>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" t="s">
         <v>7</v>
@@ -16389,7 +17035,7 @@
       </c>
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" t="s">
         <v>8</v>
@@ -16403,7 +17049,7 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" t="s">
         <v>9</v>
@@ -16416,7 +17062,7 @@
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
       <c r="B10" t="s">
         <v>10</v>
@@ -16429,10 +17075,10 @@
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
@@ -16440,48 +17086,48 @@
         <v>16</v>
       </c>
       <c r="C12">
-        <v>5.6793288970000004</v>
+        <v>5.6</v>
       </c>
       <c r="D12" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" t="s">
         <v>16</v>
       </c>
       <c r="C13">
         <f>C12/1000</f>
-        <v>5.6793288970000003E-3</v>
+        <v>5.5999999999999999E-3</v>
       </c>
       <c r="D13" t="s">
         <v>25</v>
       </c>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="B14" t="s">
         <v>17</v>
       </c>
       <c r="C14">
-        <v>238.438997</v>
+        <v>238</v>
       </c>
       <c r="D14" t="s">
         <v>26</v>
       </c>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" t="s">
         <v>17</v>
       </c>
       <c r="C15">
         <f>C14/1000</f>
-        <v>0.23843899700000001</v>
+        <v>0.23799999999999999</v>
       </c>
       <c r="D15" t="s">
         <v>25</v>
@@ -16489,17 +17135,17 @@
       <c r="E15" s="1"/>
       <c r="H15">
         <f>C15/C22</f>
-        <v>27539.704153500003</v>
+        <v>27489</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" t="s">
         <v>18</v>
       </c>
       <c r="C16">
         <f>PI()*C15*C15*C13</f>
-        <v>1.0143818390226504E-3</v>
+        <v>9.9653329591166536E-4</v>
       </c>
       <c r="D16" t="s">
         <v>24</v>
@@ -16507,14 +17153,14 @@
       <c r="E16" s="1"/>
       <c r="H16">
         <f>C13/C22</f>
-        <v>655.96248760350011</v>
+        <v>646.80000000000007</v>
       </c>
       <c r="I16">
         <f>C13/K22</f>
-        <v>226.88866418823523</v>
+        <v>223.71948208973697</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
       <c r="B17" t="s">
         <v>19</v>
@@ -16528,10 +17174,10 @@
       <c r="E17" s="2"/>
       <c r="K17">
         <f>0.8*(4+(C15/C22)+(1/100)*((C15/C22)^(2)))^(-1/2)</f>
-        <v>2.8996363972734967E-4</v>
+        <v>2.904975153790326E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" t="s">
         <v>19</v>
@@ -16545,7 +17191,7 @@
       </c>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" t="s">
         <v>20</v>
@@ -16558,10 +17204,10 @@
       </c>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>27</v>
       </c>
@@ -16577,7 +17223,7 @@
       </c>
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="B22" t="s">
         <v>71</v>
@@ -16595,10 +17241,10 @@
         <v>2.503134705878571E-5</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>30</v>
       </c>
@@ -16611,10 +17257,10 @@
       <c r="E24" s="1"/>
       <c r="M24">
         <f>0.8*((4+C15/K22)^(-1/2))</f>
-        <v>8.1950628627785859E-3</v>
+        <v>8.2026142054345951E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
       <c r="B25" t="s">
         <v>29</v>
@@ -16625,35 +17271,35 @@
       <c r="E25" s="1"/>
       <c r="M25">
         <f>0.86*((3+C13/(2*K22))^(-1/2))</f>
-        <v>7.9696504601983451E-2</v>
+        <v>8.0244363179958422E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
       <c r="B26" t="s">
         <v>31</v>
       </c>
       <c r="C26">
         <f>2*PI()*C15*C15*C25+2*PI()*C15*C13*C24</f>
-        <v>0.22309373409144201</v>
+        <v>0.22221017652954653</v>
       </c>
       <c r="E26" s="1"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
       <c r="B27" t="s">
         <v>32</v>
       </c>
       <c r="C27">
         <f>PI()*C15*C15*C13/C26</f>
-        <v>4.5468862814715986E-3</v>
+        <v>4.4846429244394205E-3</v>
       </c>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>33</v>
       </c>
@@ -16669,14 +17315,14 @@
       </c>
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="K30">
         <f>SQRT(C31)</f>
-        <v>1.4184498581197715</v>
+        <v>1.4212670403551895</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>35</v>
       </c>
@@ -16684,42 +17330,45 @@
         <v>36</v>
       </c>
       <c r="C31">
-        <v>2.012</v>
+        <v>2.02</v>
       </c>
       <c r="D31" t="s">
         <v>73</v>
       </c>
       <c r="E31" s="2"/>
+      <c r="H31">
+        <v>2.012</v>
+      </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
       <c r="B32" t="s">
         <v>37</v>
       </c>
       <c r="C32">
         <f>((C6*C31)/(C8))^(1/2)</f>
-        <v>2202.9397162387527</v>
+        <v>2207.3149732129477</v>
       </c>
       <c r="D32" t="s">
         <v>72</v>
       </c>
       <c r="E32" s="1"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
       <c r="B33" t="s">
         <v>38</v>
       </c>
       <c r="C33">
         <f>(C37/C32)*C29*C27</f>
-        <v>1.0026572574190127</v>
+        <v>1.023835398177996</v>
       </c>
       <c r="E33" s="1"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>39</v>
       </c>
@@ -16728,36 +17377,36 @@
       </c>
       <c r="C35">
         <f>(0.00000000000002336)*(C31^1.609)*(EXP(0.0618*((LN(C31))^(2))-0.117*((LN(C31))^(3))))</f>
-        <v>7.124676454802147E-14</v>
+        <v>7.1678693496010322E-14</v>
       </c>
       <c r="E35" s="1"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
       <c r="B36" t="s">
         <v>41</v>
       </c>
       <c r="C36">
         <f>(0.0000000000000248)*((C31)^(0.33))*(EXP(-12.78/C31))</f>
-        <v>5.4457627237865974E-17</v>
+        <v>5.5918117749185726E-17</v>
       </c>
       <c r="E36" s="1"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
       <c r="B37" t="s">
         <v>42</v>
       </c>
       <c r="C37">
         <f>(0.0000000000000234)*((C31)^(0.59))*(EXP(-17.44/C31))</f>
-        <v>6.0798833652813782E-18</v>
+        <v>6.3069706035286401E-18</v>
       </c>
       <c r="E37" s="1"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>43</v>
       </c>
@@ -16766,28 +17415,28 @@
       </c>
       <c r="C39">
         <f>(C37*C10+C36*C9+C35*(3*C7/C8)*C31)/(C37)</f>
-        <v>125.46954275325692</v>
+        <v>124.34002174697321</v>
       </c>
       <c r="D39" t="s">
         <v>11</v>
       </c>
       <c r="E39" s="1"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
       <c r="B40" t="s">
         <v>76</v>
       </c>
       <c r="C40">
         <f>C41+(1/2)*C31+2*C31</f>
-        <v>446.03</v>
+        <v>446.05</v>
       </c>
       <c r="D40" t="s">
         <v>11</v>
       </c>
       <c r="E40" s="1"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
       <c r="B41" s="4" t="s">
         <v>44</v>
@@ -16800,24 +17449,24 @@
       </c>
       <c r="E41" s="2"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
       <c r="B42" t="s">
         <v>77</v>
       </c>
       <c r="C42">
         <f>C40+C39</f>
-        <v>571.49954275325695</v>
+        <v>570.39002174697316</v>
       </c>
       <c r="D42" t="s">
         <v>11</v>
       </c>
       <c r="E42" s="1"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>45</v>
       </c>
@@ -16832,10 +17481,10 @@
       </c>
       <c r="E44" s="2"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>47</v>
       </c>
@@ -16844,31 +17493,31 @@
       </c>
       <c r="C46">
         <f>C44/(C6*C32*C26*C42)</f>
-        <v>2.0027034873718604E+16</v>
+        <v>2.0105846085072644E+16</v>
       </c>
       <c r="D46" t="s">
         <v>74</v>
       </c>
       <c r="E46" s="1"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
       <c r="B47" t="s">
         <v>80</v>
       </c>
       <c r="C47">
         <f>C46*0.000001</f>
-        <v>20027034873.718601</v>
+        <v>20105846085.072643</v>
       </c>
       <c r="D47" t="s">
         <v>79</v>
       </c>
       <c r="E47" s="1"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>48</v>
       </c>
@@ -16877,20 +17526,20 @@
       </c>
       <c r="C49">
         <f>C29*C35</f>
-        <v>5692603309.018856</v>
+        <v>5727114352.0701523</v>
       </c>
       <c r="D49" t="s">
         <v>51</v>
       </c>
       <c r="E49" s="1"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
       <c r="K50">
         <v>8.2452397714329748E-5</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>50</v>
       </c>
@@ -16899,17 +17548,17 @@
       </c>
       <c r="C51">
         <f>SQRT((C46*C6*C6)/(C7*C5))</f>
-        <v>7974609105.1905937</v>
+        <v>7990284703.392868</v>
       </c>
       <c r="D51" t="s">
         <v>49</v>
       </c>
       <c r="E51" s="1"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="3"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>53</v>
       </c>
@@ -16921,7 +17570,7 @@
       </c>
       <c r="E53" s="2"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>54</v>
       </c>
@@ -16934,39 +17583,39 @@
       </c>
       <c r="E54" s="1"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="3"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>55</v>
       </c>
       <c r="C56">
         <f>((C5*C49)/(((C54)^2)+((C49)^2)))*((C51)^2)</f>
-        <v>9.8846915741538297E-2</v>
+        <v>9.8638156363140592E-2</v>
       </c>
       <c r="E56" s="1"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>56</v>
       </c>
       <c r="C57">
         <f>-(((C51)^2)/(((C54)^2)+((C49)^2)))</f>
-        <v>-1.9620448528263585</v>
+        <v>-1.9461029946584865</v>
       </c>
       <c r="E57" s="1"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="3"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>57</v>
       </c>
       <c r="C59">
         <f>SQRT((C5*C4*11600*C31)/(C46*C6*C6))</f>
-        <v>7.4580994470893242E-5</v>
+        <v>7.4582513733016114E-5</v>
       </c>
       <c r="D59" t="s">
         <v>25</v>
@@ -16974,27 +17623,27 @@
       <c r="E59" s="1"/>
       <c r="K59">
         <f>743*SQRT(C31/C47)</f>
-        <v>7.4472249950558083E-3</v>
+        <v>7.4473766997486153E-3</v>
       </c>
       <c r="L59" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="3"/>
       <c r="C60">
         <f>C59*1000000</f>
-        <v>74.580994470893245</v>
+        <v>74.582513733016114</v>
       </c>
       <c r="D60" t="s">
         <v>58</v>
       </c>
       <c r="E60" s="1"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="3"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>59</v>
       </c>
@@ -17003,14 +17652,14 @@
       </c>
       <c r="C62">
         <f>C13/(C56*PI()*C15*C15)</f>
-        <v>0.32168399365851075</v>
+        <v>0.31903570785629126</v>
       </c>
       <c r="D62" t="s">
         <v>63</v>
       </c>
       <c r="E62" s="1"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>60</v>
       </c>
@@ -17019,14 +17668,14 @@
       </c>
       <c r="C63">
         <f>-1*C13/(C54*C5*C57*PI()*C15*C15)</f>
-        <v>22.592838302734862</v>
+        <v>22.5426812334731</v>
       </c>
       <c r="D63" t="s">
         <v>63</v>
       </c>
       <c r="E63" s="1"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>61</v>
       </c>
@@ -17035,14 +17684,14 @@
       </c>
       <c r="C64">
         <f>-1*C13/(C54*C5*PI()*C15*C15)</f>
-        <v>-44.328162102619146</v>
+        <v>-43.870379456093659</v>
       </c>
       <c r="D64" t="s">
         <v>63</v>
       </c>
       <c r="E64" s="1"/>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="3"/>
       <c r="F65" t="s">
         <v>137</v>
@@ -17054,7 +17703,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
         <v>62</v>
       </c>
@@ -17063,7 +17712,7 @@
       </c>
       <c r="C66">
         <f>C63/C54</f>
-        <v>2.7874123212063257E-7</v>
+        <v>2.7812241463970138E-7</v>
       </c>
       <c r="D66" t="s">
         <v>64</v>
@@ -17071,28 +17720,28 @@
       <c r="E66" s="1"/>
       <c r="F66">
         <f>2*PI()*430000*$C$66</f>
-        <v>0.75309461009116208</v>
+        <v>0.75142270778243658</v>
       </c>
       <c r="G66">
         <f>2*PI()*2000000*$C$66</f>
-        <v>3.502765628330986</v>
+        <v>3.4949893385229607</v>
       </c>
       <c r="H66">
         <f>2*PI()*12900000*$C$66</f>
-        <v>22.592838302734862</v>
+        <v>22.542681233473097</v>
       </c>
       <c r="I66" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="5"/>
       <c r="B67" t="s">
         <v>84</v>
       </c>
       <c r="C67">
         <f>C66*1000000</f>
-        <v>0.27874123212063256</v>
+        <v>0.27812241463970139</v>
       </c>
       <c r="D67" t="s">
         <v>68</v>
@@ -17111,14 +17760,14 @@
         <v>139</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="5"/>
       <c r="B68" t="s">
         <v>83</v>
       </c>
       <c r="C68">
         <f>C66*1000000000</f>
-        <v>278.74123212063256</v>
+        <v>278.12241463970139</v>
       </c>
       <c r="D68" t="s">
         <v>69</v>
@@ -17135,18 +17784,18 @@
       </c>
       <c r="K68">
         <f>F66/F69</f>
-        <v>5.6630260491269434E-4</v>
+        <v>5.7094157614514911E-4</v>
       </c>
       <c r="L68">
         <f>G66/G69</f>
-        <v>1.2251002810442278E-2</v>
+        <v>1.2351359137807445E-2</v>
       </c>
       <c r="M68">
         <f>H66/H69</f>
-        <v>0.50967234442142495</v>
+        <v>0.5138474185306342</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
         <v>13</v>
       </c>
@@ -17155,7 +17804,7 @@
       </c>
       <c r="C69">
         <f>1/(C54*-1*C64)</f>
-        <v>2.7832402478547274E-10</v>
+        <v>2.8122830576588768E-10</v>
       </c>
       <c r="D69" t="s">
         <v>65</v>
@@ -17163,15 +17812,15 @@
       <c r="E69" s="1"/>
       <c r="F69">
         <f>1/(2*PI()*430000*$C$69)</f>
-        <v>1329.8448630785745</v>
+        <v>1316.1113836828099</v>
       </c>
       <c r="G69">
         <f>1/(2*PI()*2000000*$C$69)</f>
-        <v>285.91664556189352</v>
+        <v>282.96394749180411</v>
       </c>
       <c r="H69">
         <f>1/(2*PI()*12900000*$C$69)</f>
-        <v>44.328162102619146</v>
+        <v>43.870379456093659</v>
       </c>
       <c r="I69" t="s">
         <v>135</v>
@@ -17181,20 +17830,20 @@
       </c>
       <c r="K69">
         <f>1/(2*PI()*SQRT(C66*C69))</f>
-        <v>18069418.473178223</v>
+        <v>17995860.616850719</v>
       </c>
       <c r="L69" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="5"/>
       <c r="B70" t="s">
         <v>87</v>
       </c>
       <c r="C70">
         <f>C69*1000000000</f>
-        <v>0.27832402478547275</v>
+        <v>0.2812283057658877</v>
       </c>
       <c r="D70" t="s">
         <v>66</v>
@@ -17202,27 +17851,27 @@
       <c r="E70" s="1"/>
       <c r="K70">
         <f>K69*0.000001</f>
-        <v>18.069418473178221</v>
+        <v>17.995860616850717</v>
       </c>
       <c r="L70" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="5"/>
       <c r="B71" t="s">
         <v>88</v>
       </c>
       <c r="C71">
         <f>C69*1000000000000</f>
-        <v>278.32402478547272</v>
+        <v>281.22830576588768</v>
       </c>
       <c r="D71" t="s">
         <v>67</v>
       </c>
       <c r="E71" s="1"/>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
         <v>106</v>
       </c>
@@ -17233,7 +17882,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>107</v>
       </c>
@@ -17244,29 +17893,29 @@
         <v>115</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
         <v>96</v>
       </c>
       <c r="C76">
         <f>20*C59</f>
-        <v>1.4916198894178649E-3</v>
+        <v>1.4916502746603222E-3</v>
       </c>
       <c r="D76" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="5"/>
       <c r="C77">
         <f>C76*1000000</f>
-        <v>1491.6198894178649</v>
+        <v>1491.6502746603223</v>
       </c>
       <c r="D77" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>97</v>
       </c>
@@ -17278,7 +17927,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>98</v>
       </c>
@@ -17290,77 +17939,77 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>99</v>
       </c>
       <c r="C81">
         <f>C5*C78/C76</f>
-        <v>5.5219205364809828E-10</v>
+        <v>5.5218080537514969E-10</v>
       </c>
       <c r="D81" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>113</v>
       </c>
       <c r="C82">
         <f>C81*1000000000</f>
-        <v>0.55219205364809831</v>
+        <v>0.55218080537514969</v>
       </c>
       <c r="D82" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>100</v>
       </c>
       <c r="C83">
         <f>C5*C79/C76</f>
-        <v>1.6177199815575881E-9</v>
+        <v>1.6176870282476181E-9</v>
       </c>
       <c r="D83" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>114</v>
       </c>
       <c r="C84">
         <f>C83*1000000000</f>
-        <v>1.617719981557588</v>
+        <v>1.6176870282476181</v>
       </c>
       <c r="D84" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>118</v>
       </c>
       <c r="C86">
         <f>1.95*((((2*C22)/(((PI())^2)*(((C59)^2)))*(C103/(C6*C54*C46))))^(1/2))*(C103/(C6*C54*C46))</f>
-        <v>7.3028558094956147E-4</v>
+        <v>7.2598112546906114E-4</v>
       </c>
       <c r="D86" t="s">
         <v>122</v>
       </c>
       <c r="E86">
         <f>C86*1000</f>
-        <v>0.73028558094956142</v>
+        <v>0.72598112546906113</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>123</v>
       </c>
       <c r="C87">
         <f>1.52*C5/C86</f>
-        <v>1.842019115660054E-8</v>
+        <v>1.8529407346931471E-8</v>
       </c>
       <c r="D87" t="s">
         <v>127</v>
@@ -17369,7 +18018,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="E88" t="s">
         <v>137</v>
       </c>
@@ -17392,205 +18041,205 @@
         <v>141</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>124</v>
       </c>
       <c r="C89">
         <f>C87*C78*1000000000</f>
-        <v>1.7143487707536558</v>
+        <v>1.7245134123715651</v>
       </c>
       <c r="D89" t="s">
         <v>136</v>
       </c>
       <c r="E89">
         <f>1/(2*PI()*430000*$C$89*0.000000001)</f>
-        <v>215.89992710153169</v>
+        <v>214.62736791551649</v>
       </c>
       <c r="F89">
         <f>1/(2*PI()*2000000*$C$89*0.000000001)</f>
-        <v>46.418484326829308</v>
+        <v>46.144884101836041</v>
       </c>
       <c r="G89">
         <f>1/(2*PI()*12900000*$C$89*0.000000001)</f>
-        <v>7.196664236717722</v>
+        <v>7.1542455971838832</v>
       </c>
       <c r="H89" t="s">
         <v>135</v>
       </c>
       <c r="J89">
         <f>F66/E89</f>
-        <v>3.4881651893147827E-3</v>
+        <v>3.5010572746632116E-3</v>
       </c>
       <c r="K89">
         <f t="shared" ref="K89:L89" si="0">G66/F89</f>
-        <v>7.5460577378361982E-2</v>
+        <v>7.5739475925650876E-2</v>
       </c>
       <c r="L89">
         <f t="shared" si="0"/>
-        <v>3.1393486703833049</v>
+        <v>3.1509515471968901</v>
       </c>
       <c r="N89">
         <f>1/(2*PI()*SQRT(C66*C89*0.000000001))</f>
-        <v>7280646.3096999824</v>
+        <v>7267229.0368126361</v>
       </c>
       <c r="O89" t="s">
         <v>143</v>
       </c>
       <c r="P89">
         <f>N89*0.000001</f>
-        <v>7.2806463096999821</v>
+        <v>7.267229036812636</v>
       </c>
       <c r="Q89" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>125</v>
       </c>
       <c r="C90">
         <f>C87*C79*1000000000</f>
-        <v>5.0224124803763903</v>
+        <v>5.0521911483996416</v>
       </c>
       <c r="D90" t="s">
         <v>136</v>
       </c>
       <c r="E90">
         <f>1/(2*PI()*430000*$C$90*0.000000001)</f>
-        <v>73.695216408146663</v>
+        <v>73.260841436998746</v>
       </c>
       <c r="F90">
         <f>1/(2*PI()*2000000*$C$90*0.000000001)</f>
-        <v>15.844471527751532</v>
+        <v>15.75108090895473</v>
       </c>
       <c r="G90">
         <f>1/(2*PI()*12900000*$C$90*0.000000001)</f>
-        <v>2.4565072136048887</v>
+        <v>2.4420280478999579</v>
       </c>
       <c r="H90" t="s">
         <v>135</v>
       </c>
       <c r="J90">
         <f>F66/E90</f>
-        <v>1.0219043335462828E-2</v>
+        <v>1.025681241224384E-2</v>
       </c>
       <c r="K90">
         <f t="shared" ref="K90:L90" si="1">G66/F90</f>
-        <v>0.22107178659735702</v>
+        <v>0.22188885694416094</v>
       </c>
       <c r="L90">
         <f t="shared" si="1"/>
-        <v>9.1971390019165469</v>
+        <v>9.2311311710194577</v>
       </c>
       <c r="N90">
         <f>1/(2*PI()*SQRT(C66*C90*0.000000001))</f>
-        <v>4253665.5031380933</v>
+        <v>4245826.5574731929</v>
       </c>
       <c r="O90" t="s">
         <v>143</v>
       </c>
       <c r="P90">
         <f>N90*0.000001</f>
-        <v>4.2536655031380928</v>
+        <v>4.245826557473193</v>
       </c>
       <c r="Q90" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>144</v>
       </c>
       <c r="C91">
         <f>C89+C90</f>
-        <v>6.7367612511300461</v>
+        <v>6.7767045607712069</v>
       </c>
       <c r="N91">
         <f>1/(2*PI()*SQRT(C66*C91*0.000000001))</f>
-        <v>3672771.8046473451</v>
+        <v>3666003.3696129099</v>
       </c>
       <c r="O91" t="s">
         <v>143</v>
       </c>
       <c r="P91">
         <f>N91*0.000001</f>
-        <v>3.6727718046473448</v>
+        <v>3.6660033696129095</v>
       </c>
       <c r="Q91" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>126</v>
       </c>
       <c r="C93">
         <f>2.17*((C86/C22)^(2/3))*((C6*C6*C46)/(C7*C94))*(((C59)/(C86))^(2/3))</f>
-        <v>5410.0151665771527</v>
+        <v>5420.6127648565052</v>
       </c>
       <c r="D93" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>128</v>
       </c>
       <c r="C94">
         <f>((8*C6*C31)/(PI()*C7))^(1/2)</f>
-        <v>948629.80707743682</v>
+        <v>950513.88004990621</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>129</v>
       </c>
       <c r="C95">
         <f>C93*C78</f>
-        <v>503.504701538169</v>
+        <v>504.49100941243006</v>
       </c>
       <c r="D95" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>130</v>
       </c>
       <c r="C96">
         <f>C93*C79</f>
-        <v>1475.0839152885933</v>
+        <v>1477.9734352402452</v>
       </c>
       <c r="D96" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>133</v>
       </c>
       <c r="C97">
         <f>1/C95</f>
-        <v>1.9860787733363269E-3</v>
+        <v>1.9821958792975887E-3</v>
       </c>
       <c r="D97" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>134</v>
       </c>
       <c r="C98">
         <f>1/C96</f>
-        <v>6.7792753323078206E-4</v>
+        <v>6.7660214734336515E-4</v>
       </c>
       <c r="D98" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>101</v>
       </c>
@@ -17604,7 +18253,7 @@
         <v>101.55115701055705</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>117</v>
       </c>
@@ -17615,7 +18264,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>119</v>
       </c>
@@ -17627,7 +18276,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>102</v>
       </c>
@@ -17636,7 +18285,7 @@
         <v>729.8557976234946</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>108</v>
       </c>
@@ -17645,7 +18294,7 @@
         <v>1.5989242614132864</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>109</v>
       </c>
@@ -17654,7 +18303,7 @@
         <v>91.611611940053663</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>110</v>
       </c>
@@ -17663,7 +18312,7 @@
         <v>675.12325474042757</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>111</v>
       </c>
@@ -17672,19 +18321,19 @@
         <v>361.26113315639435</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C112">
         <f>C109*(C78/(C78+C79))</f>
         <v>171.80313784718339</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C113">
         <f>C110*(C79/(C78+C79))</f>
         <v>269.32859221265085</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>103</v>
       </c>
@@ -17693,16 +18342,16 @@
         <v>441.13173005983424</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>112</v>
       </c>
       <c r="C116">
         <f>-1*C31*LN(((C8)/(2*PI()*C7))^(1/2))</f>
-        <v>-9.4140103207635875</v>
+        <v>-9.4514417733312346</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>116</v>
       </c>
@@ -17730,7 +18379,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D2E7687-BDAA-4F33-9641-B209E360CDA7}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
